--- a/NWJSSP_JuanLlorente_Noise.xlsx
+++ b/NWJSSP_JuanLlorente_Noise.xlsx
@@ -356,10 +356,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="B1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -367,19 +367,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -394,312 +394,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>6959226</v>
+        <v>6801647</v>
       </c>
       <c r="B1">
-        <v>2463</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>1419</v>
+        <v>18272</v>
       </c>
       <c r="B2">
-        <v>22758</v>
+        <v>136898</v>
       </c>
       <c r="C2">
-        <v>133723</v>
+        <v>36705</v>
       </c>
       <c r="D2">
-        <v>64820</v>
+        <v>115021</v>
       </c>
       <c r="E2">
-        <v>105989</v>
+        <v>55767</v>
       </c>
       <c r="F2">
-        <v>39229</v>
+        <v>28800</v>
       </c>
       <c r="G2">
-        <v>126967</v>
+        <v>86486</v>
       </c>
       <c r="H2">
-        <v>95761</v>
+        <v>73691</v>
       </c>
       <c r="I2">
-        <v>35030</v>
+        <v>57084</v>
       </c>
       <c r="J2">
-        <v>89868</v>
+        <v>1076</v>
       </c>
       <c r="K2">
-        <v>57277</v>
+        <v>124695</v>
       </c>
       <c r="L2">
-        <v>54592</v>
+        <v>39531</v>
       </c>
       <c r="M2">
-        <v>16384</v>
+        <v>128856</v>
       </c>
       <c r="N2">
-        <v>18840</v>
+        <v>80975</v>
       </c>
       <c r="O2">
-        <v>139619</v>
+        <v>76341</v>
       </c>
       <c r="P2">
-        <v>104540</v>
+        <v>25320</v>
       </c>
       <c r="Q2">
-        <v>117100</v>
+        <v>40592</v>
       </c>
       <c r="R2">
-        <v>82219</v>
+        <v>19222</v>
       </c>
       <c r="S2">
-        <v>123392</v>
+        <v>122020</v>
       </c>
       <c r="T2">
-        <v>13997</v>
+        <v>5133</v>
       </c>
       <c r="U2">
-        <v>95565</v>
+        <v>64308</v>
       </c>
       <c r="V2">
-        <v>49061</v>
+        <v>100439</v>
       </c>
       <c r="W2">
-        <v>64122</v>
+        <v>29743</v>
       </c>
       <c r="X2">
-        <v>17233</v>
+        <v>102302</v>
       </c>
       <c r="Y2">
-        <v>72542</v>
+        <v>105963</v>
       </c>
       <c r="Z2">
-        <v>31024</v>
+        <v>25078</v>
       </c>
       <c r="AA2">
-        <v>120957</v>
+        <v>116075</v>
       </c>
       <c r="AB2">
-        <v>84721</v>
+        <v>96458</v>
       </c>
       <c r="AC2">
-        <v>9636</v>
+        <v>32262</v>
       </c>
       <c r="AD2">
-        <v>68928</v>
+        <v>8707</v>
       </c>
       <c r="AE2">
-        <v>99704</v>
+        <v>49623</v>
       </c>
       <c r="AF2">
-        <v>26831</v>
+        <v>56058</v>
       </c>
       <c r="AG2">
-        <v>44093</v>
+        <v>99312</v>
       </c>
       <c r="AH2">
-        <v>108260</v>
+        <v>90448</v>
       </c>
       <c r="AI2">
-        <v>50855</v>
+        <v>83739</v>
       </c>
       <c r="AJ2">
-        <v>38936</v>
+        <v>91018</v>
       </c>
       <c r="AK2">
-        <v>107831</v>
+        <v>45199</v>
       </c>
       <c r="AL2">
-        <v>138544</v>
+        <v>78817</v>
       </c>
       <c r="AM2">
+        <v>145187</v>
+      </c>
+      <c r="AN2">
+        <v>125966</v>
+      </c>
+      <c r="AO2">
+        <v>104471</v>
+      </c>
+      <c r="AP2">
+        <v>100555</v>
+      </c>
+      <c r="AQ2">
+        <v>66797</v>
+      </c>
+      <c r="AR2">
+        <v>113794</v>
+      </c>
+      <c r="AS2">
+        <v>38621</v>
+      </c>
+      <c r="AT2">
+        <v>129924</v>
+      </c>
+      <c r="AU2">
+        <v>135867</v>
+      </c>
+      <c r="AV2">
+        <v>11084</v>
+      </c>
+      <c r="AW2">
+        <v>109993</v>
+      </c>
+      <c r="AX2">
+        <v>21606</v>
+      </c>
+      <c r="AY2">
+        <v>121075</v>
+      </c>
+      <c r="AZ2">
+        <v>48659</v>
+      </c>
+      <c r="BA2">
+        <v>132671</v>
+      </c>
+      <c r="BB2">
+        <v>20588</v>
+      </c>
+      <c r="BC2">
+        <v>140772</v>
+      </c>
+      <c r="BD2">
+        <v>60312</v>
+      </c>
+      <c r="BE2">
+        <v>3290</v>
+      </c>
+      <c r="BF2">
+        <v>72482</v>
+      </c>
+      <c r="BG2">
+        <v>8489</v>
+      </c>
+      <c r="BH2">
+        <v>43897</v>
+      </c>
+      <c r="BI2">
+        <v>14112</v>
+      </c>
+      <c r="BJ2">
+        <v>27070</v>
+      </c>
+      <c r="BK2">
+        <v>1314</v>
+      </c>
+      <c r="BL2">
+        <v>83252</v>
+      </c>
+      <c r="BM2">
+        <v>16406</v>
+      </c>
+      <c r="BN2">
+        <v>86853</v>
+      </c>
+      <c r="BO2">
+        <v>3433</v>
+      </c>
+      <c r="BP2">
+        <v>69047</v>
+      </c>
+      <c r="BQ2">
+        <v>63753</v>
+      </c>
+      <c r="BR2">
+        <v>6243</v>
+      </c>
+      <c r="BS2">
+        <v>61706</v>
+      </c>
+      <c r="BT2">
+        <v>13832</v>
+      </c>
+      <c r="BU2">
+        <v>10006</v>
+      </c>
+      <c r="BV2">
+        <v>334</v>
+      </c>
+      <c r="BW2">
+        <v>16834</v>
+      </c>
+      <c r="BX2">
         <v>0</v>
       </c>
-      <c r="AN2">
-        <v>4464</v>
-      </c>
-      <c r="AO2">
-        <v>33777</v>
-      </c>
-      <c r="AP2">
-        <v>83553</v>
-      </c>
-      <c r="AQ2">
-        <v>40731</v>
-      </c>
-      <c r="AR2">
-        <v>24092</v>
-      </c>
-      <c r="AS2">
-        <v>98758</v>
-      </c>
-      <c r="AT2">
-        <v>77429</v>
-      </c>
-      <c r="AU2">
-        <v>57748</v>
-      </c>
-      <c r="AV2">
-        <v>104343</v>
-      </c>
-      <c r="AW2">
-        <v>72235</v>
-      </c>
-      <c r="AX2">
-        <v>2613</v>
-      </c>
-      <c r="AY2">
-        <v>40328</v>
-      </c>
-      <c r="AZ2">
-        <v>10301</v>
-      </c>
-      <c r="BA2">
-        <v>49439</v>
-      </c>
-      <c r="BB2">
-        <v>53382</v>
-      </c>
-      <c r="BC2">
-        <v>87608</v>
-      </c>
-      <c r="BD2">
-        <v>28546</v>
-      </c>
-      <c r="BE2">
-        <v>12433</v>
-      </c>
-      <c r="BF2">
-        <v>91096</v>
-      </c>
-      <c r="BG2">
-        <v>22401</v>
-      </c>
-      <c r="BH2">
-        <v>133415</v>
-      </c>
-      <c r="BI2">
-        <v>80220</v>
-      </c>
-      <c r="BJ2">
-        <v>46669</v>
-      </c>
-      <c r="BK2">
-        <v>45588</v>
-      </c>
-      <c r="BL2">
-        <v>67622</v>
-      </c>
-      <c r="BM2">
-        <v>123019</v>
-      </c>
-      <c r="BN2">
-        <v>126845</v>
-      </c>
-      <c r="BO2">
-        <v>38097</v>
-      </c>
-      <c r="BP2">
-        <v>100791</v>
-      </c>
-      <c r="BQ2">
-        <v>24378</v>
-      </c>
-      <c r="BR2">
-        <v>82481</v>
-      </c>
-      <c r="BS2">
-        <v>86464</v>
-      </c>
-      <c r="BT2">
-        <v>111799</v>
-      </c>
-      <c r="BU2">
-        <v>33661</v>
-      </c>
-      <c r="BV2">
-        <v>114</v>
-      </c>
-      <c r="BW2">
-        <v>129824</v>
-      </c>
-      <c r="BX2">
-        <v>61012</v>
-      </c>
       <c r="BY2">
-        <v>54332</v>
+        <v>66838</v>
       </c>
       <c r="BZ2">
-        <v>10440</v>
+        <v>12298</v>
       </c>
       <c r="CA2">
-        <v>28179</v>
+        <v>46323</v>
       </c>
       <c r="CB2">
-        <v>114879</v>
+        <v>74554</v>
       </c>
       <c r="CC2">
-        <v>111282</v>
+        <v>119916</v>
       </c>
       <c r="CD2">
-        <v>13103</v>
+        <v>117019</v>
       </c>
       <c r="CE2">
-        <v>113841</v>
+        <v>90976</v>
       </c>
       <c r="CF2">
-        <v>34154</v>
+        <v>70969</v>
       </c>
       <c r="CG2">
-        <v>73608</v>
+        <v>33665</v>
       </c>
       <c r="CH2">
-        <v>22320</v>
+        <v>52252</v>
       </c>
       <c r="CI2">
-        <v>67197</v>
+        <v>108826</v>
       </c>
       <c r="CJ2">
-        <v>63168</v>
+        <v>28833</v>
       </c>
       <c r="CK2">
-        <v>6585</v>
+        <v>111309</v>
       </c>
       <c r="CL2">
-        <v>91490</v>
+        <v>51253</v>
       </c>
       <c r="CM2">
-        <v>118019</v>
+        <v>35806</v>
       </c>
       <c r="CN2">
-        <v>4794</v>
+        <v>23413</v>
       </c>
       <c r="CO2">
-        <v>77946</v>
+        <v>93987</v>
       </c>
       <c r="CP2">
-        <v>117</v>
+        <v>6899</v>
       </c>
       <c r="CQ2">
-        <v>16459</v>
+        <v>42758</v>
       </c>
       <c r="CR2">
-        <v>75798</v>
+        <v>14826</v>
       </c>
       <c r="CS2">
-        <v>121071</v>
+        <v>52066</v>
       </c>
       <c r="CT2">
-        <v>113383</v>
+        <v>34677</v>
       </c>
       <c r="CU2">
-        <v>59757</v>
+        <v>91553</v>
       </c>
       <c r="CV2">
-        <v>102835</v>
+        <v>137476</v>
       </c>
     </row>
   </sheetData>
@@ -714,312 +714,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>44310465</v>
+        <v>45485111</v>
       </c>
       <c r="B1">
-        <v>89062</v>
+        <v>42395</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>151430</v>
+        <v>498454</v>
       </c>
       <c r="B2">
-        <v>135333</v>
+        <v>376275</v>
       </c>
       <c r="C2">
-        <v>175179</v>
+        <v>183478</v>
       </c>
       <c r="D2">
-        <v>678391</v>
+        <v>184901</v>
       </c>
       <c r="E2">
-        <v>117968</v>
+        <v>102128</v>
       </c>
       <c r="F2">
-        <v>359913</v>
+        <v>749002</v>
       </c>
       <c r="G2">
-        <v>810786</v>
+        <v>471247</v>
       </c>
       <c r="H2">
-        <v>126787</v>
+        <v>190586</v>
       </c>
       <c r="I2">
-        <v>741270</v>
+        <v>887502</v>
       </c>
       <c r="J2">
-        <v>40106</v>
+        <v>533521</v>
       </c>
       <c r="K2">
-        <v>716664</v>
+        <v>538451</v>
       </c>
       <c r="L2">
-        <v>592046</v>
+        <v>154324</v>
       </c>
       <c r="M2">
-        <v>593646</v>
+        <v>416306</v>
       </c>
       <c r="N2">
-        <v>597550</v>
+        <v>598363</v>
       </c>
       <c r="O2">
-        <v>381979</v>
+        <v>367241</v>
       </c>
       <c r="P2">
-        <v>216686</v>
+        <v>472887</v>
       </c>
       <c r="Q2">
-        <v>392780</v>
+        <v>643852</v>
       </c>
       <c r="R2">
-        <v>562682</v>
+        <v>221475</v>
       </c>
       <c r="S2">
-        <v>802790</v>
+        <v>460425</v>
       </c>
       <c r="T2">
-        <v>298671</v>
+        <v>2296</v>
       </c>
       <c r="U2">
-        <v>333190</v>
+        <v>872376</v>
       </c>
       <c r="V2">
-        <v>322303</v>
+        <v>782743</v>
       </c>
       <c r="W2">
-        <v>92382</v>
+        <v>163101</v>
       </c>
       <c r="X2">
-        <v>502524</v>
+        <v>671626</v>
       </c>
       <c r="Y2">
-        <v>295128</v>
+        <v>624932</v>
       </c>
       <c r="Z2">
-        <v>417228</v>
+        <v>88684</v>
       </c>
       <c r="AA2">
-        <v>188782</v>
+        <v>593213</v>
       </c>
       <c r="AB2">
-        <v>789989</v>
+        <v>549085</v>
       </c>
       <c r="AC2">
-        <v>128876</v>
+        <v>476538</v>
       </c>
       <c r="AD2">
-        <v>262882</v>
+        <v>721543</v>
       </c>
       <c r="AE2">
-        <v>680467</v>
+        <v>72056</v>
       </c>
       <c r="AF2">
-        <v>429751</v>
+        <v>395399</v>
       </c>
       <c r="AG2">
-        <v>169644</v>
+        <v>115491</v>
       </c>
       <c r="AH2">
-        <v>48097</v>
+        <v>778173</v>
       </c>
       <c r="AI2">
-        <v>261960</v>
+        <v>62471</v>
       </c>
       <c r="AJ2">
-        <v>642688</v>
+        <v>326185</v>
       </c>
       <c r="AK2">
+        <v>68338</v>
+      </c>
+      <c r="AL2">
+        <v>150474</v>
+      </c>
+      <c r="AM2">
+        <v>448010</v>
+      </c>
+      <c r="AN2">
+        <v>133669</v>
+      </c>
+      <c r="AO2">
+        <v>19344</v>
+      </c>
+      <c r="AP2">
+        <v>49266</v>
+      </c>
+      <c r="AQ2">
         <v>0</v>
       </c>
-      <c r="AL2">
-        <v>818115</v>
-      </c>
-      <c r="AM2">
-        <v>786408</v>
-      </c>
-      <c r="AN2">
-        <v>452210</v>
-      </c>
-      <c r="AO2">
-        <v>670616</v>
-      </c>
-      <c r="AP2">
-        <v>669141</v>
-      </c>
-      <c r="AQ2">
-        <v>518986</v>
-      </c>
       <c r="AR2">
-        <v>112138</v>
+        <v>242674</v>
       </c>
       <c r="AS2">
-        <v>749968</v>
+        <v>595115</v>
       </c>
       <c r="AT2">
-        <v>162803</v>
+        <v>292663</v>
       </c>
       <c r="AU2">
-        <v>385713</v>
+        <v>414461</v>
       </c>
       <c r="AV2">
-        <v>484572</v>
+        <v>688121</v>
       </c>
       <c r="AW2">
-        <v>3977</v>
+        <v>650877</v>
       </c>
       <c r="AX2">
-        <v>435804</v>
+        <v>25074</v>
       </c>
       <c r="AY2">
-        <v>640271</v>
+        <v>823563</v>
       </c>
       <c r="AZ2">
-        <v>209509</v>
+        <v>120839</v>
       </c>
       <c r="BA2">
-        <v>305913</v>
+        <v>353424</v>
       </c>
       <c r="BB2">
-        <v>755929</v>
+        <v>837277</v>
       </c>
       <c r="BC2">
-        <v>616078</v>
+        <v>211863</v>
       </c>
       <c r="BD2">
-        <v>477187</v>
+        <v>268962</v>
       </c>
       <c r="BE2">
-        <v>246192</v>
+        <v>200335</v>
       </c>
       <c r="BF2">
-        <v>510717</v>
+        <v>860974</v>
       </c>
       <c r="BG2">
-        <v>266621</v>
+        <v>20831</v>
       </c>
       <c r="BH2">
-        <v>703592</v>
+        <v>261162</v>
       </c>
       <c r="BI2">
-        <v>524495</v>
+        <v>522403</v>
       </c>
       <c r="BJ2">
-        <v>183342</v>
+        <v>444414</v>
       </c>
       <c r="BK2">
-        <v>190552</v>
+        <v>338147</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>429971</v>
       </c>
       <c r="BM2">
-        <v>329678</v>
+        <v>564513</v>
       </c>
       <c r="BN2">
-        <v>55805</v>
+        <v>509034</v>
       </c>
       <c r="BO2">
-        <v>548481</v>
+        <v>39193</v>
       </c>
       <c r="BP2">
-        <v>365318</v>
+        <v>344715</v>
       </c>
       <c r="BQ2">
-        <v>720285</v>
+        <v>238984</v>
       </c>
       <c r="BR2">
-        <v>230880</v>
+        <v>813991</v>
       </c>
       <c r="BS2">
-        <v>217222</v>
+        <v>139943</v>
       </c>
       <c r="BT2">
-        <v>225910</v>
+        <v>244358</v>
       </c>
       <c r="BU2">
-        <v>136564</v>
+        <v>762430</v>
       </c>
       <c r="BV2">
-        <v>3927</v>
+        <v>588607</v>
       </c>
       <c r="BW2">
-        <v>553782</v>
+        <v>308084</v>
       </c>
       <c r="BX2">
-        <v>279993</v>
+        <v>715372</v>
       </c>
       <c r="BY2">
-        <v>455271</v>
+        <v>110501</v>
       </c>
       <c r="BZ2">
-        <v>829421</v>
+        <v>290794</v>
       </c>
       <c r="CA2">
-        <v>77746</v>
+        <v>634728</v>
       </c>
       <c r="CB2">
-        <v>344982</v>
+        <v>82913</v>
       </c>
       <c r="CC2">
-        <v>65855</v>
+        <v>691850</v>
       </c>
       <c r="CD2">
-        <v>571160</v>
+        <v>314722</v>
       </c>
       <c r="CE2">
-        <v>405347</v>
+        <v>850255</v>
       </c>
       <c r="CF2">
-        <v>87024</v>
+        <v>564352</v>
       </c>
       <c r="CG2">
-        <v>597292</v>
+        <v>230910</v>
       </c>
       <c r="CH2">
-        <v>467224</v>
+        <v>112744</v>
       </c>
       <c r="CI2">
-        <v>312650</v>
+        <v>378148</v>
       </c>
       <c r="CJ2">
-        <v>70853</v>
+        <v>1493</v>
       </c>
       <c r="CK2">
-        <v>18089</v>
+        <v>745182</v>
       </c>
       <c r="CL2">
-        <v>657786</v>
+        <v>851154</v>
       </c>
       <c r="CM2">
-        <v>535954</v>
+        <v>808144</v>
       </c>
       <c r="CN2">
-        <v>430773</v>
+        <v>678424</v>
       </c>
       <c r="CO2">
-        <v>348656</v>
+        <v>170592</v>
       </c>
       <c r="CP2">
-        <v>7202</v>
+        <v>548282</v>
       </c>
       <c r="CQ2">
-        <v>613670</v>
+        <v>219681</v>
       </c>
       <c r="CR2">
-        <v>733751</v>
+        <v>338519</v>
       </c>
       <c r="CS2">
-        <v>40232</v>
+        <v>271319</v>
       </c>
       <c r="CT2">
-        <v>763195</v>
+        <v>296898</v>
       </c>
       <c r="CU2">
-        <v>454504</v>
+        <v>516630</v>
       </c>
       <c r="CV2">
-        <v>815918</v>
+        <v>690403</v>
       </c>
     </row>
   </sheetData>
@@ -1034,312 +1034,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>45465490</v>
+        <v>44363479</v>
       </c>
       <c r="B1">
-        <v>84200</v>
+        <v>42905</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>393512</v>
+        <v>516841</v>
       </c>
       <c r="B2">
-        <v>575122</v>
+        <v>359264</v>
       </c>
       <c r="C2">
-        <v>705637</v>
+        <v>189115</v>
       </c>
       <c r="D2">
-        <v>718893</v>
+        <v>164557</v>
       </c>
       <c r="E2">
-        <v>46323</v>
+        <v>92347</v>
       </c>
       <c r="F2">
-        <v>756870</v>
+        <v>564760</v>
       </c>
       <c r="G2">
-        <v>157237</v>
+        <v>482295</v>
       </c>
       <c r="H2">
-        <v>174</v>
+        <v>396009</v>
       </c>
       <c r="I2">
-        <v>649085</v>
+        <v>848781</v>
       </c>
       <c r="J2">
-        <v>754279</v>
+        <v>618969</v>
       </c>
       <c r="K2">
-        <v>220767</v>
+        <v>430152</v>
       </c>
       <c r="L2">
-        <v>688406</v>
+        <v>259846</v>
       </c>
       <c r="M2">
-        <v>107308</v>
+        <v>125323</v>
       </c>
       <c r="N2">
-        <v>450768</v>
+        <v>528457</v>
       </c>
       <c r="O2">
-        <v>334803</v>
+        <v>350935</v>
       </c>
       <c r="P2">
-        <v>339774</v>
+        <v>511347</v>
       </c>
       <c r="Q2">
+        <v>713206</v>
+      </c>
+      <c r="R2">
+        <v>234039</v>
+      </c>
+      <c r="S2">
+        <v>406860</v>
+      </c>
+      <c r="T2">
+        <v>803</v>
+      </c>
+      <c r="U2">
+        <v>836307</v>
+      </c>
+      <c r="V2">
+        <v>775870</v>
+      </c>
+      <c r="W2">
+        <v>419760</v>
+      </c>
+      <c r="X2">
+        <v>664010</v>
+      </c>
+      <c r="Y2">
+        <v>620167</v>
+      </c>
+      <c r="Z2">
+        <v>54483</v>
+      </c>
+      <c r="AA2">
+        <v>539810</v>
+      </c>
+      <c r="AB2">
+        <v>185082</v>
+      </c>
+      <c r="AC2">
+        <v>352894</v>
+      </c>
+      <c r="AD2">
+        <v>429544</v>
+      </c>
+      <c r="AE2">
+        <v>70033</v>
+      </c>
+      <c r="AF2">
+        <v>1334</v>
+      </c>
+      <c r="AG2">
+        <v>113013</v>
+      </c>
+      <c r="AH2">
+        <v>757624</v>
+      </c>
+      <c r="AI2">
+        <v>29385</v>
+      </c>
+      <c r="AJ2">
+        <v>312222</v>
+      </c>
+      <c r="AK2">
+        <v>377726</v>
+      </c>
+      <c r="AL2">
+        <v>115987</v>
+      </c>
+      <c r="AM2">
+        <v>431799</v>
+      </c>
+      <c r="AN2">
+        <v>69548</v>
+      </c>
+      <c r="AO2">
+        <v>177683</v>
+      </c>
+      <c r="AP2">
+        <v>50078</v>
+      </c>
+      <c r="AQ2">
+        <v>57280</v>
+      </c>
+      <c r="AR2">
+        <v>121561</v>
+      </c>
+      <c r="AS2">
+        <v>229287</v>
+      </c>
+      <c r="AT2">
+        <v>286210</v>
+      </c>
+      <c r="AU2">
+        <v>450749</v>
+      </c>
+      <c r="AV2">
+        <v>696950</v>
+      </c>
+      <c r="AW2">
+        <v>633548</v>
+      </c>
+      <c r="AX2">
+        <v>12857</v>
+      </c>
+      <c r="AY2">
+        <v>793322</v>
+      </c>
+      <c r="AZ2">
+        <v>155140</v>
+      </c>
+      <c r="BA2">
+        <v>236116</v>
+      </c>
+      <c r="BB2">
+        <v>807477</v>
+      </c>
+      <c r="BC2">
+        <v>485073</v>
+      </c>
+      <c r="BD2">
+        <v>310423</v>
+      </c>
+      <c r="BE2">
+        <v>198990</v>
+      </c>
+      <c r="BF2">
+        <v>849492</v>
+      </c>
+      <c r="BG2">
+        <v>21439</v>
+      </c>
+      <c r="BH2">
+        <v>255525</v>
+      </c>
+      <c r="BI2">
+        <v>467539</v>
+      </c>
+      <c r="BJ2">
+        <v>499344</v>
+      </c>
+      <c r="BK2">
+        <v>441789</v>
+      </c>
+      <c r="BL2">
+        <v>374530</v>
+      </c>
+      <c r="BM2">
+        <v>535544</v>
+      </c>
+      <c r="BN2">
+        <v>578520</v>
+      </c>
+      <c r="BO2">
+        <v>78852</v>
+      </c>
+      <c r="BP2">
+        <v>201932</v>
+      </c>
+      <c r="BQ2">
+        <v>228196</v>
+      </c>
+      <c r="BR2">
+        <v>731694</v>
+      </c>
+      <c r="BS2">
+        <v>141982</v>
+      </c>
+      <c r="BT2">
+        <v>397793</v>
+      </c>
+      <c r="BU2">
+        <v>750546</v>
+      </c>
+      <c r="BV2">
+        <v>608915</v>
+      </c>
+      <c r="BW2">
+        <v>626198</v>
+      </c>
+      <c r="BX2">
+        <v>665044</v>
+      </c>
+      <c r="BY2">
+        <v>558549</v>
+      </c>
+      <c r="BZ2">
+        <v>339726</v>
+      </c>
+      <c r="CA2">
+        <v>581389</v>
+      </c>
+      <c r="CB2">
+        <v>131841</v>
+      </c>
+      <c r="CC2">
+        <v>686587</v>
+      </c>
+      <c r="CD2">
+        <v>312221</v>
+      </c>
+      <c r="CE2">
+        <v>726885</v>
+      </c>
+      <c r="CF2">
+        <v>473752</v>
+      </c>
+      <c r="CG2">
+        <v>82045</v>
+      </c>
+      <c r="CH2">
+        <v>100164</v>
+      </c>
+      <c r="CI2">
+        <v>325901</v>
+      </c>
+      <c r="CJ2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>190411</v>
-      </c>
-      <c r="S2">
-        <v>610452</v>
-      </c>
-      <c r="T2">
-        <v>316999</v>
-      </c>
-      <c r="U2">
-        <v>499872</v>
-      </c>
-      <c r="V2">
-        <v>682148</v>
-      </c>
-      <c r="W2">
-        <v>528101</v>
-      </c>
-      <c r="X2">
-        <v>38649</v>
-      </c>
-      <c r="Y2">
-        <v>323661</v>
-      </c>
-      <c r="Z2">
-        <v>562834</v>
-      </c>
-      <c r="AA2">
-        <v>367310</v>
-      </c>
-      <c r="AB2">
-        <v>810918</v>
-      </c>
-      <c r="AC2">
-        <v>422809</v>
-      </c>
-      <c r="AD2">
-        <v>484389</v>
-      </c>
-      <c r="AE2">
-        <v>152630</v>
-      </c>
-      <c r="AF2">
-        <v>44286</v>
-      </c>
-      <c r="AG2">
-        <v>1892</v>
-      </c>
-      <c r="AH2">
-        <v>84459</v>
-      </c>
-      <c r="AI2">
-        <v>203434</v>
-      </c>
-      <c r="AJ2">
-        <v>369980</v>
-      </c>
-      <c r="AK2">
-        <v>544368</v>
-      </c>
-      <c r="AL2">
-        <v>279247</v>
-      </c>
-      <c r="AM2">
-        <v>824356</v>
-      </c>
-      <c r="AN2">
-        <v>579853</v>
-      </c>
-      <c r="AO2">
-        <v>549571</v>
-      </c>
-      <c r="AP2">
-        <v>381759</v>
-      </c>
-      <c r="AQ2">
-        <v>869049</v>
-      </c>
-      <c r="AR2">
-        <v>712413</v>
-      </c>
-      <c r="AS2">
-        <v>296663</v>
-      </c>
-      <c r="AT2">
-        <v>326495</v>
-      </c>
-      <c r="AU2">
-        <v>163398</v>
-      </c>
-      <c r="AV2">
-        <v>251121</v>
-      </c>
-      <c r="AW2">
-        <v>692693</v>
-      </c>
-      <c r="AX2">
-        <v>438682</v>
-      </c>
-      <c r="AY2">
-        <v>79933</v>
-      </c>
-      <c r="AZ2">
-        <v>135176</v>
-      </c>
-      <c r="BA2">
-        <v>770791</v>
-      </c>
-      <c r="BB2">
-        <v>777217</v>
-      </c>
-      <c r="BC2">
-        <v>270251</v>
-      </c>
-      <c r="BD2">
-        <v>737869</v>
-      </c>
-      <c r="BE2">
-        <v>573362</v>
-      </c>
-      <c r="BF2">
-        <v>822201</v>
-      </c>
-      <c r="BG2">
-        <v>116161</v>
-      </c>
-      <c r="BH2">
-        <v>377362</v>
-      </c>
-      <c r="BI2">
-        <v>29648</v>
-      </c>
-      <c r="BJ2">
-        <v>65785</v>
-      </c>
-      <c r="BK2">
-        <v>535883</v>
-      </c>
-      <c r="BL2">
-        <v>5462</v>
-      </c>
-      <c r="BM2">
-        <v>277125</v>
-      </c>
-      <c r="BN2">
-        <v>79114</v>
-      </c>
-      <c r="BO2">
-        <v>154199</v>
-      </c>
-      <c r="BP2">
-        <v>667285</v>
-      </c>
-      <c r="BQ2">
-        <v>796890</v>
-      </c>
-      <c r="BR2">
-        <v>270073</v>
-      </c>
-      <c r="BS2">
-        <v>625050</v>
-      </c>
-      <c r="BT2">
-        <v>318856</v>
-      </c>
-      <c r="BU2">
-        <v>227961</v>
-      </c>
-      <c r="BV2">
-        <v>200337</v>
-      </c>
-      <c r="BW2">
-        <v>275411</v>
-      </c>
-      <c r="BX2">
-        <v>481051</v>
-      </c>
-      <c r="BY2">
-        <v>474550</v>
-      </c>
-      <c r="BZ2">
-        <v>8669</v>
-      </c>
-      <c r="CA2">
-        <v>408853</v>
-      </c>
-      <c r="CB2">
-        <v>847364</v>
-      </c>
-      <c r="CC2">
-        <v>666868</v>
-      </c>
-      <c r="CD2">
-        <v>123499</v>
-      </c>
-      <c r="CE2">
-        <v>111242</v>
-      </c>
-      <c r="CF2">
-        <v>217930</v>
-      </c>
-      <c r="CG2">
-        <v>611552</v>
-      </c>
-      <c r="CH2">
-        <v>605161</v>
-      </c>
-      <c r="CI2">
-        <v>178457</v>
-      </c>
-      <c r="CJ2">
-        <v>408801</v>
-      </c>
       <c r="CK2">
-        <v>849772</v>
+        <v>705085</v>
       </c>
       <c r="CL2">
-        <v>344134</v>
+        <v>818894</v>
       </c>
       <c r="CM2">
-        <v>434751</v>
+        <v>776344</v>
       </c>
       <c r="CN2">
-        <v>233846</v>
+        <v>651504</v>
       </c>
       <c r="CO2">
-        <v>615479</v>
+        <v>213350</v>
       </c>
       <c r="CP2">
-        <v>532424</v>
+        <v>598423</v>
       </c>
       <c r="CQ2">
-        <v>512217</v>
+        <v>274350</v>
       </c>
       <c r="CR2">
-        <v>444861</v>
+        <v>647860</v>
       </c>
       <c r="CS2">
-        <v>641183</v>
+        <v>294433</v>
       </c>
       <c r="CT2">
-        <v>75111</v>
+        <v>227321</v>
       </c>
       <c r="CU2">
-        <v>747653</v>
+        <v>573060</v>
       </c>
       <c r="CV2">
-        <v>198132</v>
+        <v>157005</v>
       </c>
     </row>
   </sheetData>
@@ -1354,10 +1354,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1365,19 +1365,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>15</v>
       </c>
       <c r="D2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1392,42 +1392,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>10743</v>
+        <v>10676</v>
       </c>
       <c r="B1">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2">
-        <v>1017</v>
+        <v>194</v>
       </c>
       <c r="C2">
-        <v>690</v>
+        <v>952</v>
       </c>
       <c r="D2">
-        <v>1090</v>
+        <v>1406</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c r="G2">
-        <v>440</v>
+        <v>236</v>
       </c>
       <c r="H2">
-        <v>124</v>
+        <v>589</v>
       </c>
       <c r="I2">
-        <v>1345</v>
+        <v>1130</v>
       </c>
       <c r="J2">
-        <v>605</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -1442,42 +1442,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>11091</v>
+        <v>12852</v>
       </c>
       <c r="B1">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>849</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="C2">
-        <v>571</v>
+        <v>1212</v>
       </c>
       <c r="D2">
-        <v>956</v>
+        <v>1719</v>
       </c>
       <c r="E2">
-        <v>1569</v>
+        <v>419</v>
       </c>
       <c r="F2">
-        <v>166</v>
+        <v>289</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="H2">
-        <v>402</v>
+        <v>1049</v>
       </c>
       <c r="I2">
-        <v>263</v>
+        <v>1443</v>
       </c>
       <c r="J2">
-        <v>1197</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -1492,72 +1492,72 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1">
-        <v>21239</v>
+        <v>19484</v>
       </c>
       <c r="B1">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>682</v>
+        <v>75</v>
       </c>
       <c r="B2">
-        <v>143</v>
+        <v>1412</v>
       </c>
       <c r="C2">
-        <v>1531</v>
+        <v>912</v>
       </c>
       <c r="D2">
-        <v>1415</v>
+        <v>727</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>577</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="H2">
-        <v>769</v>
+        <v>27</v>
       </c>
       <c r="I2">
-        <v>1818</v>
+        <v>1113</v>
       </c>
       <c r="J2">
-        <v>1220</v>
+        <v>1560</v>
       </c>
       <c r="K2">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="L2">
-        <v>1086</v>
+        <v>303</v>
       </c>
       <c r="M2">
-        <v>291</v>
+        <v>670</v>
       </c>
       <c r="N2">
-        <v>800</v>
+        <v>1706</v>
       </c>
       <c r="O2">
-        <v>1120</v>
+        <v>570</v>
       </c>
       <c r="P2">
-        <v>1711</v>
+        <v>898</v>
       </c>
       <c r="Q2">
-        <v>609</v>
+        <v>422</v>
       </c>
       <c r="R2">
-        <v>1219</v>
+        <v>1559</v>
       </c>
       <c r="S2">
-        <v>460</v>
+        <v>1281</v>
       </c>
       <c r="T2">
-        <v>878</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1572,72 +1572,72 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1">
-        <v>20184</v>
+        <v>19797</v>
       </c>
       <c r="B1">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>1043</v>
+        <v>152</v>
       </c>
       <c r="B2">
-        <v>1074</v>
+        <v>1321</v>
       </c>
       <c r="C2">
-        <v>398</v>
+        <v>1044</v>
       </c>
       <c r="D2">
-        <v>282</v>
+        <v>744</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>132</v>
+        <v>594</v>
       </c>
       <c r="G2">
-        <v>620</v>
+        <v>299</v>
       </c>
       <c r="H2">
-        <v>694</v>
+        <v>27</v>
       </c>
       <c r="I2">
-        <v>1829</v>
+        <v>1245</v>
       </c>
       <c r="J2">
-        <v>771</v>
+        <v>1677</v>
       </c>
       <c r="K2">
-        <v>36</v>
+        <v>392</v>
       </c>
       <c r="L2">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="M2">
-        <v>1647</v>
+        <v>683</v>
       </c>
       <c r="N2">
-        <v>1130</v>
+        <v>1823</v>
       </c>
       <c r="O2">
-        <v>1547</v>
+        <v>583</v>
       </c>
       <c r="P2">
-        <v>171</v>
+        <v>915</v>
       </c>
       <c r="Q2">
-        <v>806</v>
+        <v>435</v>
       </c>
       <c r="R2">
-        <v>1357</v>
+        <v>1466</v>
       </c>
       <c r="S2">
-        <v>898</v>
+        <v>953</v>
       </c>
       <c r="T2">
-        <v>598</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1652,42 +1652,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>111363</v>
+        <v>115032</v>
       </c>
       <c r="B1">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>712</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>2031</v>
+        <v>9678</v>
       </c>
       <c r="C2">
-        <v>9498</v>
+        <v>136</v>
       </c>
       <c r="D2">
-        <v>3026</v>
+        <v>6008</v>
       </c>
       <c r="E2">
-        <v>6541</v>
+        <v>4072</v>
       </c>
       <c r="F2">
-        <v>11367</v>
+        <v>14606</v>
       </c>
       <c r="G2">
-        <v>4477</v>
+        <v>2008</v>
       </c>
       <c r="H2">
-        <v>13480</v>
+        <v>8645</v>
       </c>
       <c r="I2">
-        <v>7476</v>
+        <v>10715</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>6409</v>
       </c>
     </row>
   </sheetData>
@@ -1702,42 +1702,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>104078</v>
+        <v>114972</v>
       </c>
       <c r="B1">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>6053</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>5715</v>
+        <v>3426</v>
       </c>
       <c r="C2">
-        <v>4121</v>
+        <v>2700</v>
       </c>
       <c r="D2">
-        <v>11768</v>
+        <v>13282</v>
       </c>
       <c r="E2">
-        <v>10282</v>
+        <v>6982</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11468</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>837</v>
       </c>
       <c r="H2">
-        <v>5090</v>
+        <v>9145</v>
       </c>
       <c r="I2">
-        <v>7763</v>
+        <v>4463</v>
       </c>
       <c r="J2">
-        <v>531</v>
+        <v>9914</v>
       </c>
     </row>
   </sheetData>
@@ -1752,312 +1752,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>7011649</v>
+        <v>6675102</v>
       </c>
       <c r="B1">
-        <v>2428</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>36008</v>
+        <v>4122</v>
       </c>
       <c r="B2">
-        <v>106460</v>
+        <v>123674</v>
       </c>
       <c r="C2">
-        <v>45077</v>
+        <v>26219</v>
       </c>
       <c r="D2">
-        <v>26630</v>
+        <v>114434</v>
       </c>
       <c r="E2">
-        <v>81994</v>
+        <v>58242</v>
       </c>
       <c r="F2">
-        <v>72967</v>
+        <v>29885</v>
       </c>
       <c r="G2">
-        <v>67819</v>
+        <v>67492</v>
       </c>
       <c r="H2">
-        <v>6431</v>
+        <v>71319</v>
       </c>
       <c r="I2">
+        <v>35178</v>
+      </c>
+      <c r="J2">
+        <v>7360</v>
+      </c>
+      <c r="K2">
+        <v>109267</v>
+      </c>
+      <c r="L2">
+        <v>42873</v>
+      </c>
+      <c r="M2">
+        <v>137702</v>
+      </c>
+      <c r="N2">
+        <v>77741</v>
+      </c>
+      <c r="O2">
+        <v>82206</v>
+      </c>
+      <c r="P2">
+        <v>23428</v>
+      </c>
+      <c r="Q2">
+        <v>39068</v>
+      </c>
+      <c r="R2">
+        <v>22548</v>
+      </c>
+      <c r="S2">
+        <v>109420</v>
+      </c>
+      <c r="T2">
+        <v>9764</v>
+      </c>
+      <c r="U2">
+        <v>76942</v>
+      </c>
+      <c r="V2">
+        <v>124027</v>
+      </c>
+      <c r="W2">
+        <v>14381</v>
+      </c>
+      <c r="X2">
+        <v>92312</v>
+      </c>
+      <c r="Y2">
+        <v>87508</v>
+      </c>
+      <c r="Z2">
+        <v>16699</v>
+      </c>
+      <c r="AA2">
+        <v>72140</v>
+      </c>
+      <c r="AB2">
+        <v>109697</v>
+      </c>
+      <c r="AC2">
+        <v>33705</v>
+      </c>
+      <c r="AD2">
+        <v>7250</v>
+      </c>
+      <c r="AE2">
+        <v>53858</v>
+      </c>
+      <c r="AF2">
+        <v>61825</v>
+      </c>
+      <c r="AG2">
+        <v>73850</v>
+      </c>
+      <c r="AH2">
+        <v>117820</v>
+      </c>
+      <c r="AI2">
+        <v>80880</v>
+      </c>
+      <c r="AJ2">
+        <v>104247</v>
+      </c>
+      <c r="AK2">
+        <v>38352</v>
+      </c>
+      <c r="AL2">
+        <v>75206</v>
+      </c>
+      <c r="AM2">
+        <v>141238</v>
+      </c>
+      <c r="AN2">
+        <v>116554</v>
+      </c>
+      <c r="AO2">
+        <v>86016</v>
+      </c>
+      <c r="AP2">
+        <v>31820</v>
+      </c>
+      <c r="AQ2">
+        <v>54699</v>
+      </c>
+      <c r="AR2">
+        <v>98809</v>
+      </c>
+      <c r="AS2">
+        <v>41718</v>
+      </c>
+      <c r="AT2">
+        <v>64776</v>
+      </c>
+      <c r="AU2">
+        <v>131145</v>
+      </c>
+      <c r="AV2">
+        <v>9836</v>
+      </c>
+      <c r="AW2">
+        <v>97259</v>
+      </c>
+      <c r="AX2">
+        <v>68042</v>
+      </c>
+      <c r="AY2">
+        <v>126025</v>
+      </c>
+      <c r="AZ2">
+        <v>39700</v>
+      </c>
+      <c r="BA2">
+        <v>103460</v>
+      </c>
+      <c r="BB2">
+        <v>19183</v>
+      </c>
+      <c r="BC2">
+        <v>134918</v>
+      </c>
+      <c r="BD2">
+        <v>50819</v>
+      </c>
+      <c r="BE2">
+        <v>4923</v>
+      </c>
+      <c r="BF2">
+        <v>48089</v>
+      </c>
+      <c r="BG2">
+        <v>12806</v>
+      </c>
+      <c r="BH2">
+        <v>101830</v>
+      </c>
+      <c r="BI2">
+        <v>25250</v>
+      </c>
+      <c r="BJ2">
+        <v>27615</v>
+      </c>
+      <c r="BK2">
+        <v>1639</v>
+      </c>
+      <c r="BL2">
+        <v>90238</v>
+      </c>
+      <c r="BM2">
+        <v>19795</v>
+      </c>
+      <c r="BN2">
+        <v>83163</v>
+      </c>
+      <c r="BO2">
+        <v>1347</v>
+      </c>
+      <c r="BP2">
+        <v>57479</v>
+      </c>
+      <c r="BQ2">
+        <v>59507</v>
+      </c>
+      <c r="BR2">
+        <v>3351</v>
+      </c>
+      <c r="BS2">
+        <v>47638</v>
+      </c>
+      <c r="BT2">
+        <v>20686</v>
+      </c>
+      <c r="BU2">
+        <v>14199</v>
+      </c>
+      <c r="BV2">
+        <v>52540</v>
+      </c>
+      <c r="BW2">
+        <v>91020</v>
+      </c>
+      <c r="BX2">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>96083</v>
-      </c>
-      <c r="K2">
-        <v>57192</v>
-      </c>
-      <c r="L2">
-        <v>60474</v>
-      </c>
-      <c r="M2">
-        <v>19185</v>
-      </c>
-      <c r="N2">
-        <v>100744</v>
-      </c>
-      <c r="O2">
-        <v>66284</v>
-      </c>
-      <c r="P2">
-        <v>55410</v>
-      </c>
-      <c r="Q2">
-        <v>68453</v>
-      </c>
-      <c r="R2">
-        <v>17184</v>
-      </c>
-      <c r="S2">
-        <v>142694</v>
-      </c>
-      <c r="T2">
-        <v>75799</v>
-      </c>
-      <c r="U2">
-        <v>12213</v>
-      </c>
-      <c r="V2">
-        <v>84138</v>
-      </c>
-      <c r="W2">
-        <v>42539</v>
-      </c>
-      <c r="X2">
-        <v>139916</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>64276</v>
-      </c>
-      <c r="AA2">
-        <v>30270</v>
-      </c>
-      <c r="AB2">
-        <v>4772</v>
-      </c>
-      <c r="AC2">
-        <v>99352</v>
-      </c>
-      <c r="AD2">
-        <v>76308</v>
-      </c>
-      <c r="AE2">
-        <v>96062</v>
-      </c>
-      <c r="AF2">
-        <v>72697</v>
-      </c>
-      <c r="AG2">
-        <v>121817</v>
-      </c>
-      <c r="AH2">
-        <v>45735</v>
-      </c>
-      <c r="AI2">
-        <v>126725</v>
-      </c>
-      <c r="AJ2">
-        <v>62754</v>
-      </c>
-      <c r="AK2">
-        <v>71356</v>
-      </c>
-      <c r="AL2">
-        <v>13389</v>
-      </c>
-      <c r="AM2">
-        <v>119162</v>
-      </c>
-      <c r="AN2">
-        <v>45797</v>
-      </c>
-      <c r="AO2">
-        <v>133229</v>
-      </c>
-      <c r="AP2">
-        <v>135895</v>
-      </c>
-      <c r="AQ2">
-        <v>137152</v>
-      </c>
-      <c r="AR2">
-        <v>14513</v>
-      </c>
-      <c r="AS2">
-        <v>123354</v>
-      </c>
-      <c r="AT2">
-        <v>131248</v>
-      </c>
-      <c r="AU2">
-        <v>114387</v>
-      </c>
-      <c r="AV2">
-        <v>25936</v>
-      </c>
-      <c r="AW2">
-        <v>85266</v>
-      </c>
-      <c r="AX2">
-        <v>16902</v>
-      </c>
-      <c r="AY2">
-        <v>108990</v>
-      </c>
-      <c r="AZ2">
-        <v>51243</v>
-      </c>
-      <c r="BA2">
-        <v>36481</v>
-      </c>
-      <c r="BB2">
-        <v>142970</v>
-      </c>
-      <c r="BC2">
-        <v>40092</v>
-      </c>
-      <c r="BD2">
-        <v>3801</v>
-      </c>
-      <c r="BE2">
-        <v>90455</v>
-      </c>
-      <c r="BF2">
-        <v>114010</v>
-      </c>
-      <c r="BG2">
-        <v>38769</v>
-      </c>
-      <c r="BH2">
-        <v>103716</v>
-      </c>
-      <c r="BI2">
-        <v>20242</v>
-      </c>
-      <c r="BJ2">
-        <v>60060</v>
-      </c>
-      <c r="BK2">
-        <v>40419</v>
-      </c>
-      <c r="BL2">
-        <v>48503</v>
-      </c>
-      <c r="BM2">
-        <v>80530</v>
-      </c>
-      <c r="BN2">
-        <v>29476</v>
-      </c>
-      <c r="BO2">
-        <v>5112</v>
-      </c>
-      <c r="BP2">
-        <v>31830</v>
-      </c>
-      <c r="BQ2">
-        <v>92222</v>
-      </c>
-      <c r="BR2">
-        <v>128981</v>
-      </c>
-      <c r="BS2">
-        <v>77859</v>
-      </c>
-      <c r="BT2">
-        <v>35602</v>
-      </c>
-      <c r="BU2">
-        <v>80128</v>
-      </c>
-      <c r="BV2">
-        <v>109587</v>
-      </c>
-      <c r="BW2">
-        <v>90832</v>
-      </c>
-      <c r="BX2">
-        <v>24128</v>
-      </c>
       <c r="BY2">
-        <v>93198</v>
+        <v>19898</v>
       </c>
       <c r="BZ2">
-        <v>22708</v>
+        <v>12080</v>
       </c>
       <c r="CA2">
-        <v>40966</v>
+        <v>64007</v>
       </c>
       <c r="CB2">
-        <v>51794</v>
+        <v>65791</v>
       </c>
       <c r="CC2">
-        <v>116637</v>
+        <v>94641</v>
       </c>
       <c r="CD2">
-        <v>9091</v>
+        <v>121775</v>
       </c>
       <c r="CE2">
-        <v>65145</v>
+        <v>106467</v>
       </c>
       <c r="CF2">
-        <v>104050</v>
+        <v>68561</v>
       </c>
       <c r="CG2">
-        <v>58689</v>
+        <v>83931</v>
       </c>
       <c r="CH2">
-        <v>50630</v>
+        <v>53916</v>
       </c>
       <c r="CI2">
-        <v>84880</v>
+        <v>113271</v>
       </c>
       <c r="CJ2">
-        <v>52808</v>
+        <v>31293</v>
       </c>
       <c r="CK2">
-        <v>6158</v>
+        <v>130113</v>
       </c>
       <c r="CL2">
-        <v>119581</v>
+        <v>47836</v>
       </c>
       <c r="CM2">
-        <v>33159</v>
+        <v>36120</v>
       </c>
       <c r="CN2">
-        <v>26765</v>
+        <v>14486</v>
       </c>
       <c r="CO2">
-        <v>111667</v>
+        <v>95612</v>
       </c>
       <c r="CP2">
-        <v>9765</v>
+        <v>9080</v>
       </c>
       <c r="CQ2">
-        <v>88046</v>
+        <v>45855</v>
       </c>
       <c r="CR2">
-        <v>117</v>
+        <v>1220</v>
       </c>
       <c r="CS2">
-        <v>3676</v>
+        <v>77830</v>
       </c>
       <c r="CT2">
-        <v>70458</v>
+        <v>28040</v>
       </c>
       <c r="CU2">
-        <v>96727</v>
+        <v>99084</v>
       </c>
       <c r="CV2">
-        <v>54022</v>
+        <v>137596</v>
       </c>
     </row>
   </sheetData>
